--- a/data/trans_dic/P32A-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32A-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le ha molestado que le criticasen la forma de beber</t>
+          <t>Población a la que le ha molestado que le criticasen la forma de beber (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,19</t>
+          <t>0,6; 2,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,22</t>
+          <t>1,78; 5,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,5</t>
+          <t>2,31; 6,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 7,39</t>
+          <t>2,75; 7,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,25</t>
+          <t>0,0; 5,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,46</t>
+          <t>0,45; 2,41</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,65</t>
+          <t>1,23; 3,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,55</t>
+          <t>2,0; 5,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,85</t>
+          <t>2,33; 6,29</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,78</t>
+          <t>0,62; 1,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,96</t>
+          <t>2,02; 4,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,71</t>
+          <t>1,21; 2,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,93</t>
+          <t>0,57; 1,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,84</t>
+          <t>0,66; 3,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,58</t>
+          <t>0,28; 1,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,71</t>
+          <t>0,43; 2,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,29</t>
+          <t>0,44; 1,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,16</t>
+          <t>1,72; 3,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,06</t>
+          <t>0,94; 2,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,98</t>
+          <t>0,69; 1,9</t>
         </is>
       </c>
     </row>
@@ -997,42 +997,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,61</t>
+          <t>0,84; 3,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,94</t>
+          <t>1,13; 5,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,06</t>
+          <t>0,55; 3,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,36</t>
+          <t>0,16; 1,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,09</t>
+          <t>0,72; 2,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,73</t>
+          <t>0,87; 2,91</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,65</t>
+          <t>0,64; 1,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,41</t>
+          <t>1,87; 3,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,71</t>
+          <t>1,46; 2,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,48</t>
+          <t>1,24; 2,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,68</t>
+          <t>0,39; 1,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,19</t>
+          <t>0,75; 2,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,38</t>
+          <t>0,65; 2,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,23</t>
+          <t>0,55; 1,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,58</t>
+          <t>1,51; 2,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,31</t>
+          <t>1,36; 2,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,2</t>
+          <t>1,17; 2,19</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le ha molestado que le criticasen la forma de beber</t>
+          <t>Población a la que le ha molestado que le criticasen la forma de beber (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2678; 15011</t>
+          <t>2837; 14007</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8812; 26614</t>
+          <t>9061; 27388</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8374; 23345</t>
+          <t>8304; 23963</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6649; 17968</t>
+          <t>6697; 18109</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4621</t>
+          <t>0; 4379</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2064</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 8380</t>
+          <t>0; 7875</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2606</t>
+          <t>0; 2935</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3161; 15695</t>
+          <t>2887; 15416</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8589; 26967</t>
+          <t>9075; 26675</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10204; 27355</t>
+          <t>9840; 27444</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7208; 18164</t>
+          <t>7241; 19531</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6046; 18877</t>
+          <t>6595; 19587</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23616; 47303</t>
+          <t>24064; 49716</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14806; 33968</t>
+          <t>15141; 34920</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5611; 18970</t>
+          <t>5599; 19175</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5974</t>
+          <t>0; 5087</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3189; 16821</t>
+          <t>3887; 17843</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1116; 11511</t>
+          <t>2007; 11542</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2639; 19076</t>
+          <t>3041; 19020</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6782; 20609</t>
+          <t>7049; 21221</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>29577; 56426</t>
+          <t>30743; 56920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19530; 40845</t>
+          <t>18720; 41071</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11759; 33465</t>
+          <t>11700; 31983</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5742</t>
+          <t>0; 6210</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6376</t>
+          <t>0; 5926</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 6661</t>
+          <t>0; 7018</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2607; 12381</t>
+          <t>2882; 12409</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5298</t>
+          <t>0; 5496</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4463</t>
+          <t>0; 4617</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3344; 16614</t>
+          <t>3168; 15435</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1279; 7380</t>
+          <t>1332; 7592</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>847; 7863</t>
+          <t>845; 7866</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>849; 7456</t>
+          <t>855; 7485</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5378; 20336</t>
+          <t>4702; 18220</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5325; 15930</t>
+          <t>5077; 16998</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12904; 30978</t>
+          <t>11965; 29959</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39636; 69143</t>
+          <t>38050; 68753</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27683; 53914</t>
+          <t>29140; 54328</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19986; 38858</t>
+          <t>19455; 39540</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>924; 7924</t>
+          <t>920; 7988</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4015; 17596</t>
+          <t>4072; 18124</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8527; 25088</t>
+          <t>8571; 25927</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6846; 24171</t>
+          <t>6626; 24492</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15185; 34160</t>
+          <t>15277; 35166</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46775; 79173</t>
+          <t>46313; 80244</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40608; 72432</t>
+          <t>42540; 72805</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29602; 56669</t>
+          <t>30118; 56466</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32A-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32A-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,97</t>
+          <t>0,58; 2,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,37</t>
+          <t>1,69; 5,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,67</t>
+          <t>2,39; 6,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,44</t>
+          <t>2,63; 7,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,88</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,41</t>
+          <t>0,6; 2,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,61</t>
+          <t>1,2; 3,74</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,57</t>
+          <t>2,02; 5,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,29</t>
+          <t>2,09; 5,59</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,85</t>
+          <t>0,63; 1,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,16</t>
+          <t>1,93; 3,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,78</t>
+          <t>1,16; 2,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,95</t>
+          <t>0,6; 1,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,01</t>
+          <t>0,68; 2,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,58</t>
+          <t>0,28; 1,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,7</t>
+          <t>1,33; 4,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,33</t>
+          <t>0,43; 1,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,19</t>
+          <t>1,7; 3,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,07</t>
+          <t>0,95; 2,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,9</t>
+          <t>1,01; 2,38</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,62</t>
+          <t>1,01; 3,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 5,52</t>
+          <t>1,11; 5,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,15</t>
+          <t>0,58; 3,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,45</t>
+          <t>0,15; 1,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,36</t>
+          <t>0,16; 1,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,77</t>
+          <t>0,72; 2,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,91</t>
+          <t>1,13; 3,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,59</t>
+          <t>0,66; 1,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,39</t>
+          <t>1,92; 3,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,52</t>
+          <t>1,31; 2,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,89</t>
+          <t>0,1; 0,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,74</t>
+          <t>0,37; 1,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,27</t>
+          <t>0,77; 2,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,42</t>
+          <t>1,29; 3,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,27</t>
+          <t>0,55; 1,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,61</t>
+          <t>1,5; 2,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,32</t>
+          <t>1,34; 2,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,19</t>
+          <t>1,44; 2,54</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11215</t>
+          <t>11076</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>888</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>11964</t>
         </is>
       </c>
     </row>
@@ -1504,27 +1504,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2837; 14007</t>
+          <t>2709; 14015</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9061; 27388</t>
+          <t>8617; 27472</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8304; 23963</t>
+          <t>8588; 23430</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6697; 18109</t>
+          <t>6783; 18277</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4379</t>
+          <t>0; 4703</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1534,32 +1534,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7875</t>
+          <t>0; 9024</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2935</t>
+          <t>0; 3079</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2887; 15416</t>
+          <t>3832; 16514</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9075; 26675</t>
+          <t>8845; 27698</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9840; 27444</t>
+          <t>9954; 26896</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7241; 19531</t>
+          <t>6944; 18592</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>11636</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20317</t>
+          <t>25735</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6595; 19587</t>
+          <t>6642; 19063</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24064; 49716</t>
+          <t>23095; 47186</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15141; 34920</t>
+          <t>14523; 34608</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5599; 19175</t>
+          <t>6240; 20016</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5087</t>
+          <t>0; 5473</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3887; 17843</t>
+          <t>3998; 16365</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2007; 11542</t>
+          <t>2022; 11594</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3041; 19020</t>
+          <t>7396; 25679</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7049; 21221</t>
+          <t>6849; 21395</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30743; 56920</t>
+          <t>30373; 61021</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18720; 41071</t>
+          <t>18905; 40985</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11700; 31983</t>
+          <t>16160; 38062</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>7723</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9699</t>
+          <t>12111</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6210</t>
+          <t>0; 5899</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5926</t>
+          <t>0; 6859</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7018</t>
+          <t>0; 7248</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2882; 12409</t>
+          <t>3708; 13968</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5496</t>
+          <t>0; 5547</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4617</t>
+          <t>0; 5015</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3168; 15435</t>
+          <t>3106; 15874</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1332; 7592</t>
+          <t>1532; 9309</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>845; 7866</t>
+          <t>836; 7602</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>855; 7485</t>
+          <t>863; 7665</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4702; 18220</t>
+          <t>4765; 18083</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5077; 16998</t>
+          <t>7141; 19783</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27988</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42084</t>
+          <t>49810</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11965; 29959</t>
+          <t>12346; 29693</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>38050; 68753</t>
+          <t>39006; 70503</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29140; 54328</t>
+          <t>29104; 54286</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19455; 39540</t>
+          <t>21739; 41208</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>920; 7988</t>
+          <t>924; 8006</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4072; 18124</t>
+          <t>3822; 17226</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8571; 25927</t>
+          <t>8765; 25510</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6626; 24492</t>
+          <t>11529; 31610</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15277; 35166</t>
+          <t>15380; 35509</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46313; 80244</t>
+          <t>46183; 79347</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42540; 72805</t>
+          <t>42061; 73571</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30118; 56466</t>
+          <t>36803; 65054</t>
         </is>
       </c>
     </row>
